--- a/data/Operations_Dataset_Dirty.xlsx
+++ b/data/Operations_Dataset_Dirty.xlsx
@@ -1,27 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\Ellicium\DW assignment - Loparex\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C13589E-B66F-4F60-B3BF-4A95727FBFC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="66">
+  <si>
+    <t>Department</t>
+  </si>
   <si>
     <t>ProcessName</t>
   </si>
   <si>
-    <t>Department</t>
-  </si>
-  <si>
     <t>DowntimeHours</t>
   </si>
   <si>
@@ -31,56 +37,194 @@
     <t>Location</t>
   </si>
   <si>
-    <t>Cutting</t>
-  </si>
-  <si>
-    <t>cutting</t>
-  </si>
-  <si>
-    <t>Assembling</t>
-  </si>
-  <si>
-    <t>Packing</t>
-  </si>
-  <si>
-    <t>ops</t>
+    <t>Legal</t>
+  </si>
+  <si>
+    <t>Finance</t>
   </si>
   <si>
     <t>Operations</t>
   </si>
   <si>
-    <t>operations</t>
-  </si>
-  <si>
-    <t>OPS</t>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>Server Maintenance</t>
+  </si>
+  <si>
+    <t>Security Audit</t>
+  </si>
+  <si>
+    <t>Inventory Check</t>
+  </si>
+  <si>
+    <t>Data Backup</t>
+  </si>
+  <si>
+    <t>System Upgrade</t>
+  </si>
+  <si>
+    <t>2023-09-01</t>
+  </si>
+  <si>
+    <t>2023-02-08</t>
+  </si>
+  <si>
+    <t>2023-07-21</t>
+  </si>
+  <si>
+    <t>2023-01-31</t>
+  </si>
+  <si>
+    <t>2023-04-03</t>
+  </si>
+  <si>
+    <t>2023-03-13</t>
+  </si>
+  <si>
+    <t>2023-08-14</t>
+  </si>
+  <si>
+    <t>2023-07-11</t>
+  </si>
+  <si>
+    <t>2023-06-15</t>
+  </si>
+  <si>
+    <t>2023-02-17</t>
+  </si>
+  <si>
+    <t>2023-11-07</t>
+  </si>
+  <si>
+    <t>2023-08-05</t>
+  </si>
+  <si>
+    <t>2023-09-10</t>
+  </si>
+  <si>
+    <t>2023-03-06</t>
+  </si>
+  <si>
+    <t>2023-07-23</t>
+  </si>
+  <si>
+    <t>2023-02-27</t>
+  </si>
+  <si>
+    <t>2023-10-06</t>
+  </si>
+  <si>
+    <t>2023-11-18</t>
+  </si>
+  <si>
+    <t>2023-06-21</t>
+  </si>
+  <si>
+    <t>2023-01-19</t>
+  </si>
+  <si>
+    <t>2023-10-01</t>
+  </si>
+  <si>
+    <t>2023-10-25</t>
+  </si>
+  <si>
+    <t>2023-10-31</t>
+  </si>
+  <si>
+    <t>2023-04-06</t>
+  </si>
+  <si>
+    <t>2023-10-13</t>
+  </si>
+  <si>
+    <t>2023-11-19</t>
+  </si>
+  <si>
+    <t>2023-03-28</t>
+  </si>
+  <si>
+    <t>2023-11-13</t>
+  </si>
+  <si>
+    <t>2023-05-06</t>
+  </si>
+  <si>
+    <t>2023-08-16</t>
+  </si>
+  <si>
+    <t>2023-01-18</t>
+  </si>
+  <si>
+    <t>2023-03-14</t>
+  </si>
+  <si>
+    <t>2023-11-20</t>
+  </si>
+  <si>
+    <t>2023-08-23</t>
+  </si>
+  <si>
+    <t>2023-03-07</t>
+  </si>
+  <si>
+    <t>2023-01-07</t>
+  </si>
+  <si>
+    <t>2023-11-22</t>
+  </si>
+  <si>
+    <t>2023-12-20</t>
+  </si>
+  <si>
+    <t>2023-09-20</t>
+  </si>
+  <si>
+    <t>2023-07-12</t>
+  </si>
+  <si>
+    <t>2023-07-06</t>
+  </si>
+  <si>
+    <t>2023-05-14</t>
+  </si>
+  <si>
+    <t>2023-07-16</t>
+  </si>
+  <si>
+    <t>2023-10-19</t>
   </si>
   <si>
     <t>2023-02-10</t>
   </si>
   <si>
-    <t>2023-02-11</t>
-  </si>
-  <si>
-    <t>2023/02/12</t>
-  </si>
-  <si>
-    <t>12-02-2023</t>
-  </si>
-  <si>
-    <t>Plant A</t>
-  </si>
-  <si>
-    <t>Plant B</t>
-  </si>
-  <si>
-    <t>Plant C</t>
+    <t>Warehouse</t>
+  </si>
+  <si>
+    <t>Remot Site A</t>
+  </si>
+  <si>
+    <t>Remote Site A</t>
+  </si>
+  <si>
+    <t>Remote Site B</t>
+  </si>
+  <si>
+    <t>HQ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -143,13 +287,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -187,7 +339,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -221,6 +373,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -255,9 +408,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -430,11 +584,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E51"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.36328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -451,86 +612,845 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2">
-        <v>2.5</v>
+        <v>5.09</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3">
-        <v>2.5</v>
+        <v>5.47</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
       <c r="C4">
-        <v>1</v>
+        <v>2.69</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6">
+        <v>7.66</v>
+      </c>
+      <c r="E6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>1.79</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8">
+        <v>2.4</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>3.28</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>4.79</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12">
+        <v>5.47</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13">
+        <v>3.47</v>
+      </c>
+      <c r="D13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14">
+        <v>5.59</v>
+      </c>
+      <c r="D14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15">
+        <v>6.85</v>
+      </c>
+      <c r="D15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16">
+        <v>7.71</v>
+      </c>
+      <c r="D16" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="D17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18">
+        <v>2.9</v>
+      </c>
+      <c r="D18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" t="s">
         <v>12</v>
       </c>
-      <c r="D5" t="s">
+      <c r="C19">
+        <v>3.03</v>
+      </c>
+      <c r="D19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20">
+        <v>6.07</v>
+      </c>
+      <c r="D20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21">
+        <v>3.53</v>
+      </c>
+      <c r="D21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" t="s">
         <v>15</v>
       </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23">
+        <v>7.14</v>
+      </c>
+      <c r="D23" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24">
+        <v>3.1</v>
+      </c>
+      <c r="D24" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25">
+        <v>3.13</v>
+      </c>
+      <c r="D25" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26">
+        <v>1.91</v>
+      </c>
+      <c r="D26" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27">
+        <v>3.87</v>
+      </c>
+      <c r="D27" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>8</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B28" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28">
+        <v>7.57</v>
+      </c>
+      <c r="D28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29">
+        <v>5.55</v>
+      </c>
+      <c r="D29" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>9</v>
       </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
+      <c r="B30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30">
+        <v>3.05</v>
+      </c>
+      <c r="D30" t="s">
+        <v>41</v>
+      </c>
+      <c r="E30" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31">
+        <v>0.6</v>
+      </c>
+      <c r="D31" t="s">
+        <v>42</v>
+      </c>
+      <c r="E31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32">
+        <v>7.1</v>
+      </c>
+      <c r="D32" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33">
+        <v>1.76</v>
+      </c>
+      <c r="D33" t="s">
+        <v>44</v>
+      </c>
+      <c r="E33" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34">
+        <v>1.63</v>
+      </c>
+      <c r="D34" t="s">
+        <v>45</v>
+      </c>
+      <c r="E34" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35">
+        <v>1.72</v>
+      </c>
+      <c r="D35" t="s">
+        <v>46</v>
+      </c>
+      <c r="E35" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36">
+        <v>6.14</v>
+      </c>
+      <c r="D36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E36" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37">
+        <v>4.21</v>
+      </c>
+      <c r="D37" t="s">
+        <v>46</v>
+      </c>
+      <c r="E37" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38">
+        <v>5.69</v>
+      </c>
+      <c r="D38" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39">
+        <v>6.55</v>
+      </c>
+      <c r="D39" t="s">
+        <v>49</v>
+      </c>
+      <c r="E39" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40">
+        <v>5.07</v>
+      </c>
+      <c r="D40" t="s">
+        <v>50</v>
+      </c>
+      <c r="E40" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>8</v>
+      </c>
+      <c r="B41" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41">
+        <v>3.76</v>
+      </c>
+      <c r="D41" t="s">
+        <v>51</v>
+      </c>
+      <c r="E41" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>10</v>
+      </c>
+      <c r="B42" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42">
+        <v>4.88</v>
+      </c>
+      <c r="D42" t="s">
+        <v>52</v>
+      </c>
+      <c r="E42" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43">
+        <v>3.12</v>
+      </c>
+      <c r="D43" t="s">
+        <v>53</v>
+      </c>
+      <c r="E43" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44">
+        <v>3.25</v>
+      </c>
+      <c r="D44" t="s">
+        <v>54</v>
+      </c>
+      <c r="E44" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="D45" t="s">
+        <v>55</v>
+      </c>
+      <c r="E45" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46">
+        <v>6.1</v>
+      </c>
+      <c r="D46" t="s">
+        <v>56</v>
+      </c>
+      <c r="E46" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47">
+        <v>3.72</v>
+      </c>
+      <c r="D47" t="s">
+        <v>57</v>
+      </c>
+      <c r="E47" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" t="s">
+        <v>13</v>
+      </c>
+      <c r="C48">
+        <v>7.48</v>
+      </c>
+      <c r="D48" t="s">
+        <v>58</v>
+      </c>
+      <c r="E48" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>10</v>
+      </c>
+      <c r="B49" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49">
+        <v>1.6</v>
+      </c>
+      <c r="D49" t="s">
+        <v>25</v>
+      </c>
+      <c r="E49" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>8</v>
+      </c>
+      <c r="B50" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50">
+        <v>4.41</v>
+      </c>
+      <c r="D50" t="s">
+        <v>59</v>
+      </c>
+      <c r="E50" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>6</v>
+      </c>
+      <c r="B51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51">
+        <v>6.33</v>
+      </c>
+      <c r="D51" t="s">
+        <v>60</v>
+      </c>
+      <c r="E51" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
